--- a/artfynd/A 7331-2025 artfynd.xlsx
+++ b/artfynd/A 7331-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1280,64 +1280,52 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>55855148</v>
+        <v>16778359</v>
       </c>
       <c r="B7" t="n">
-        <v>106707</v>
+        <v>89170</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220204</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Snörom 200 m VNV (*slåtterfibbla* /plant/), Srm</t>
+          <t>S Klockarberget, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>679375.8363424262</v>
+        <v>679366.8785861828</v>
       </c>
       <c r="R7" t="n">
-        <v>6543763.489082186</v>
+        <v>6543745.009770129</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1362,14 +1350,9 @@
           <t>Muskö</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>AB-Han-0142</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-06-29</t>
+          <t>2014-10-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1379,7 +1362,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-06-29</t>
+          <t>2014-10-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1387,156 +1370,28 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 delförekomster, den andra på1633168, 6543858</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>motionsstig</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Rolf Wahlström, Henry Gudmundson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>16778359</v>
-      </c>
-      <c r="B8" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>3215</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Rödgul trumpetsvamp</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Craterellus lutescens</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>S Klockarberget, Srm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>679366.8785861828</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6543745.009770129</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Muskö</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2014-10-23</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2014-10-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
           <t>Bo Törnquist</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
